--- a/threagile/output/cloud-native/risks.xlsx
+++ b/threagile/output/cloud-native/risks.xlsx
@@ -10,75 +10,75 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$37</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$84</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="423">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
   <si>
     <t>Function</t>
   </si>
   <si>
-    <t>Justification</t>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Severity</t>
   </si>
   <si>
     <t>Likelihood</t>
   </si>
   <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>CWE</t>
   </si>
   <si>
     <t>Action</t>
   </si>
   <si>
-    <t>Severity</t>
-  </si>
-  <si>
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -103,7 +103,7 @@
     <t/>
   </si>
   <si>
-    <t>39</t>
+    <t>21</t>
   </si>
   <si>
     <t>Exposed Default Credentials: MinIO Object Storage is tagged as intentional-misconfiguration and stores confidential data</t>
@@ -144,7 +144,7 @@
     <t>PostgreSQL Connection</t>
   </si>
   <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>SQL/NoSQL-Injection risk at API Server against database PostgreSQL Database via PostgreSQL Connection</t>
@@ -180,12 +180,332 @@
     <t>Likely</t>
   </si>
   <si>
+    <t>Repudiation</t>
+  </si>
+  <si>
+    <t>CWE-778</t>
+  </si>
+  <si>
+    <t>Cloud Audit - High-Value Cloud Service Without Audit Logging</t>
+  </si>
+  <si>
+    <t>AWS API Gateway</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>No Audit Logging: high-value cloud asset AWS API Gateway lacks audit logging for confidential data access</t>
+  </si>
+  <si>
+    <t>Enable audit logging on all high-value cloud services and route logs to a tamper-resistant sink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable data plane logging for all high-value cloud services: S3 server access logging, RDS audit log, Lambda invocation logging, API Gateway access logging. Route all logs to a centralized, immutable log sink (CloudWatch Logs with log protection, GCS bucket with object lock). Set up anomaly alerts on admin actions. Tag the asset has-audit-logging once logging is verified.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is audit logging enabled for all access (read and write) to this high-value service? Are logs shipped to a tamper-resistant centralized log store?
+</t>
+  </si>
+  <si>
+    <t>cloud-no-audit-logging-high-value@aws-api-gateway</t>
+  </si>
+  <si>
+    <t>AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>No Audit Logging: high-value cloud asset AWS RDS PostgreSQL lacks audit logging for confidential data access</t>
+  </si>
+  <si>
+    <t>cloud-no-audit-logging-high-value@rds-postgresql</t>
+  </si>
+  <si>
+    <t>AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>No Audit Logging: high-value cloud asset AWS S3 Notes Bucket lacks audit logging for confidential data access</t>
+  </si>
+  <si>
+    <t>cloud-no-audit-logging-high-value@s3-notes-bucket</t>
+  </si>
+  <si>
+    <t>Lambda Email Notifier</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>No Audit Logging: high-value cloud asset Lambda Email Notifier lacks audit logging for confidential data access</t>
+  </si>
+  <si>
+    <t>cloud-no-audit-logging-high-value@lambda-notifier</t>
+  </si>
+  <si>
+    <t>No Audit Logging: high-value cloud asset MinIO Object Storage lacks audit logging for confidential data access</t>
+  </si>
+  <si>
+    <t>cloud-no-audit-logging-high-value@minio-storage</t>
+  </si>
+  <si>
+    <t>CWE-1104</t>
+  </si>
+  <si>
+    <t>Cloud Container - Container Platform Without Image Vulnerability Scanning</t>
+  </si>
+  <si>
+    <t>ECS Container Platform</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>No Image Scanning: container platform ECS Container Platform does not have image vulnerability scanning configured</t>
+  </si>
+  <si>
+    <t>Enable image scanning in the container registry and gate deployments on scan results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable automatic vulnerability scanning in the container registry (ECR enhanced scanning, GCR Container Analysis, ACR Defender). Integrate scan results into the CI/CD pipeline and block deployment of images with critical or high CVEs without an accepted exception. Run Trivy or Grype in the CI pipeline as an additional gate. Tag the asset has-image-scanning once scanning is enabled and enforced.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is vulnerability scanning enabled in the container registry used by this platform? Are deployments blocked when the scan finds critical or high CVEs?
+</t>
+  </si>
+  <si>
+    <t>cloud-container-no-image-scanning@ecs-platform</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECR Enhanced Scanning (Inspector v2) is being evaluated. Basic ECR scanning is enabled but does not cover OS packages comprehensively. Enhanced scanning with critical/high gate in the CI pipeline is planned for sprint 22.
+</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>Security Team</t>
+  </si>
+  <si>
+    <t>VAULT-136</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>CWE-284</t>
+  </si>
+  <si>
+    <t>Cloud Container - Container Registry Publicly Accessible</t>
+  </si>
+  <si>
+    <t>AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Public Container Registry: registry AWS ECR Container Registry allows unauthenticated image pulls from the internet</t>
+  </si>
+  <si>
+    <t>Restrict container registry access to authenticated principals within the VPC or organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disable public pull access on the container registry. Require IAM authentication for all registry operations. Use VPC endpoint policies to restrict registry access to known VPC CIDRs. Audit existing images for embedded secrets with tools like Trufflehog or Gitleaks. Tag the asset has-private-registry once access is restricted.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the container registry configured to require IAM authentication for all pulls? Is public access blocked at the registry and account level?
+</t>
+  </si>
+  <si>
+    <t>cloud-container-registry-public@container-registry</t>
+  </si>
+  <si>
+    <t>CWE-312</t>
+  </si>
+  <si>
+    <t>Cloud Data - Managed Database Without Encryption at Rest</t>
+  </si>
+  <si>
+    <t>Managed DB No Encryption: database AWS RDS PostgreSQL lacks encryption at rest</t>
+  </si>
+  <si>
+    <t>Enable transparent data encryption on all managed databases storing sensitive data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable encryption at rest on the managed database: RDS/Aurora encrypt-at-rest, GCP Cloud SQL Disk Encryption, Azure SQL Transparent Data Encryption. Prefer customer-managed KMS keys for databases storing strictly-confidential data. Set the asset's encryption field to transparent (or higher) to reflect this state.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is encryption at rest enabled on the database instance and its automated snapshots? Are customer-managed keys used for databases with strictly-confidential data?
+</t>
+  </si>
+  <si>
+    <t>cloud-managed-db-no-encryption@rds-postgresql</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDS encryption cannot be enabled on an existing instance — requires snapshot + restore with encryption enabled. This is planned as a maintenance window operation in Q3 2026. Customer-managed KMS key (CMK) will be used for the strictly-confidential classification level.
+</t>
+  </si>
+  <si>
+    <t>Infrastructure Team</t>
+  </si>
+  <si>
+    <t>VAULT-135</t>
+  </si>
+  <si>
+    <t>Denial of Service</t>
+  </si>
+  <si>
+    <t>CWE-770</t>
+  </si>
+  <si>
+    <t>Cloud Network - API Gateway Without Rate Limiting</t>
+  </si>
+  <si>
+    <t>API Gateway No Rate Limiting: API gateway AWS API Gateway has no rate limiting configured</t>
+  </si>
+  <si>
+    <t>Configure per-client rate limiting on all API gateway routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure usage plans or throttling policies on the API gateway. Apply per-route and per-API-key rate limits matching the expected legitimate peak load. Add IP-based throttling via WAF for unauthenticated endpoints. Set burst limits to prevent sudden quota exhaustion. Tag the asset has-rate-limiting once configured.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are rate limits configured per route and per client on this API gateway? Are authentication endpoints subject to tighter per-IP throttling?
+</t>
+  </si>
+  <si>
+    <t>cloud-api-gateway-no-rate-limiting@aws-api-gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS API Gateway usage plan with per-IP throttling is planned for sprint 23. Current mitigation: application-level account lockout after 10 failed logins. WAF association (VAULT-135) is a separate workstream.
+</t>
+  </si>
+  <si>
+    <t>VAULT-133</t>
+  </si>
+  <si>
+    <t>CWE-693</t>
+  </si>
+  <si>
+    <t>Cloud Network - Internet-Facing API Gateway Without WAF Protection</t>
+  </si>
+  <si>
+    <t>API Gateway No WAF: internet-facing API gateway AWS API Gateway lacks WAF protection</t>
+  </si>
+  <si>
+    <t>Attach a WAF (AWS WAF, Azure Front Door WAF, GCP Cloud Armor) to all internet-facing API gateways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attach a managed WAF to the API gateway with at minimum the OWASP Core Rule Set enabled. Enable rate-limiting rules to throttle credential stuffing and scraping. Enable logging of all blocked requests. Tag the asset has-waf once the WAF is attached and the rule set is verified in enforcement (not detection-only) mode.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is a WAF attached to this API gateway in enforcement mode? Are OWASP CRS rules enabled and actively blocking requests?
+</t>
+  </si>
+  <si>
+    <t>cloud-api-gateway-no-waf@aws-api-gateway</t>
+  </si>
+  <si>
+    <t>Elevation of Privilege</t>
+  </si>
+  <si>
+    <t>CWE-250</t>
+  </si>
+  <si>
+    <t>Cloud Serverless - Function Execution Role Without Least-Privilege Restrictions</t>
+  </si>
+  <si>
+    <t>Serverless Overpermissive Role: function Lambda Email Notifier execution role is not scoped to least privilege</t>
+  </si>
+  <si>
+    <t>Apply least-privilege IAM policies to all serverless function execution roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a dedicated execution role per function with only the specific actions and resource ARNs required. Use IAM Access Analyzer to generate least-privilege policies from CloudTrail. Avoid attaching AWS-managed policies like ReadOnlyAccess or PowerUserAccess to function roles. Tag the asset has-restricted-execution-role once the policy is scoped to specific resources.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the function execution role grant only the minimum required permissions? Are all resource ARNs specific (not "*") in the role's inline and attached policies?
+</t>
+  </si>
+  <si>
+    <t>cloud-serverless-overpermissive-role@lambda-notifier</t>
+  </si>
+  <si>
+    <t>CWE-390</t>
+  </si>
+  <si>
+    <t>Cloud Serverless - Function Without Dead Letter Queue for PII Processing</t>
+  </si>
+  <si>
+    <t>Serverless No DLQ: function Lambda Email Notifier processes personal data without a dead letter queue</t>
+  </si>
+  <si>
+    <t>Configure a dead letter queue on all serverless functions processing personal data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure an SQS DLQ (or Azure Service Bus / GCP Pub/Sub dead-letter topic) on the event source mapping for all functions that process PII. Set the maximum retry count to a low value (2-3) to limit duplicate processing. Monitor DLQ depth and alert when messages are delivered to it. Tag the asset has-dlq once configured.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is a DLQ configured on the event source that triggers this function? Are DLQ depth alarms set up to notify the operations team?
+</t>
+  </si>
+  <si>
+    <t>cloud-serverless-no-dlq@lambda-notifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQS DLQ configuration is on the Lambda function backlog. Currently failed notification events are silently dropped. DLQ with CloudWatch depth alarm is planned alongside the DPA review for SES (VAULT-136).
+</t>
+  </si>
+  <si>
+    <t>VAULT-134</t>
+  </si>
+  <si>
+    <t>Cloud Storage - Object Storage Without Encryption at Rest</t>
+  </si>
+  <si>
+    <t>Unencrypted Object Storage: bucket MinIO Object Storage stores sensitive data without encryption at rest</t>
+  </si>
+  <si>
+    <t>Enable server-side encryption (SSE) on all object storage buckets holding sensitive data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable server-side encryption on the bucket using either provider-managed keys (SSE-S3 / Google-managed / Azure SSE) or customer-managed keys (SSE-KMS / CMEK). For highest assurance, use customer-managed KMS keys with key usage logging. Set the asset's encryption field to transparent or higher to reflect this state.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is server-side encryption enabled on the bucket? Are customer-managed KMS keys used for confidential or sensitive workloads?
+</t>
+  </si>
+  <si>
+    <t>cloud-object-storage-no-encryption@minio-storage</t>
+  </si>
+  <si>
+    <t>Unencrypted Object Storage: bucket AWS S3 Notes Bucket stores sensitive data without encryption at rest</t>
+  </si>
+  <si>
+    <t>cloud-object-storage-no-encryption@s3-notes-bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSE-KMS is planned alongside the RDS encryption work (VAULT-135). S3 default encryption will use a dedicated CMK for the notes bucket. Compensating control: S3 Block Public Access is enabled; bucket policy restricts access to the API ECS task role only.
+</t>
+  </si>
+  <si>
     <t>Lateral Movement</t>
   </si>
   <si>
-    <t>Architecture</t>
-  </si>
-  <si>
     <t>CWE-0</t>
   </si>
   <si>
@@ -195,7 +515,7 @@
     <t>Nginx Reverse Proxy</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t>Lateral Movement via Shared Runtime on Docker Host: assets from 3 trust zones co-located</t>
@@ -213,9 +533,6 @@
     <t>lateral-movement-shared-runtime@docker-host</t>
   </si>
   <si>
-    <t>Elevation of Privilege</t>
-  </si>
-  <si>
     <t>CWE-306</t>
   </si>
   <si>
@@ -237,6 +554,15 @@
     <t>missing-authentication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
   </si>
   <si>
+    <t>Route to ECS API</t>
+  </si>
+  <si>
+    <t>Missing Authentication covering communication link Route to ECS API from AWS API Gateway to API Server</t>
+  </si>
+  <si>
+    <t>missing-authentication@aws-api-gateway&gt;route-to-ecs-api@aws-api-gateway@api-server</t>
+  </si>
+  <si>
     <t>Unlikely</t>
   </si>
   <si>
@@ -252,19 +578,28 @@
     <t>0</t>
   </si>
   <si>
+    <t>Missing Cloud Hardening (AWS) risk at AWS Cloud: CIS Benchmark for AWS</t>
+  </si>
+  <si>
+    <t>Cloud Hardening</t>
+  </si>
+  <si>
+    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@aws-cloud@aws</t>
+  </si>
+  <si>
     <t>Missing Cloud Hardening risk at Docker Host</t>
   </si>
   <si>
-    <t>Cloud Hardening</t>
-  </si>
-  <si>
-    <t>Apply hardening of all cloud components and services, taking special care to follow the individual risk descriptions (which depend on the cloud provider tags in the model). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Amazon Web Services&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"PacBot", "CloudSploit", "CloudMapper", "ScoutSuite", or "Prowler AWS CIS Benchmark Tool"&lt;/i&gt;). &lt;br&gt;For EC2 and other servers running Amazon Linux, follow the &lt;i&gt;CIS Benchmark for Amazon Linux&lt;/i&gt; and switch to IMDSv2. &lt;br&gt;For S3 buckets follow the &lt;i&gt;Security Best Practices for Amazon S3&lt;/i&gt; at &lt;a href="https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html"&gt;https://docs.aws.amazon.com/AmazonS3/latest/dev/security-best-practices.html&lt;/a&gt; to avoid accidental leakage. &lt;br&gt;Also take a look at some of these tools: &lt;a href="https://github.com/toniblyx/my-arsenal-of-aws-security-tools"&gt;https://github.com/toniblyx/my-arsenal-of-aws-security-tools&lt;/a&gt; &lt;br&gt;&lt;br&gt;For &lt;b&gt;Microsoft Azure&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Microsoft Azure&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;).&lt;br&gt;&lt;br&gt;For &lt;b&gt;Google Cloud Platform&lt;/b&gt;: Follow the &lt;i&gt;CIS Benchmark for Google Cloud Computing Platform&lt;/i&gt; (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit" or "ScoutSuite"&lt;/i&gt;). &lt;br&gt;&lt;br&gt;For &lt;b&gt;Oracle Cloud Platform&lt;/b&gt;: Follow the hardening best practices (see also the automated checks of cloud audit tools like &lt;i&gt;"CloudSploit"&lt;/i&gt;).</t>
-  </si>
-  <si>
     <t>missing-cloud-hardening@docker-host</t>
   </si>
   <si>
-    <t>CWE-693</t>
+    <t>Missing Cloud Hardening risk at External CI/CD</t>
+  </si>
+  <si>
+    <t>missing-cloud-hardening@external-cicd</t>
   </si>
   <si>
     <t>Missing Content-Security-Policy Header on Web Entry Point</t>
@@ -293,7 +628,7 @@
     <t>Missing Hardening</t>
   </si>
   <si>
-    <t>Missing Hardening risk at API Server</t>
+    <t>Missing Hardening risk at AWS RDS PostgreSQL</t>
   </si>
   <si>
     <t>System Hardening</t>
@@ -302,73 +637,160 @@
     <t>Try to apply all hardening best practices (like CIS benchmarks, OWASP recommendations, vendor recommendations, DevSec Hardening Framework, DBSAT for Oracle databases, and others).</t>
   </si>
   <si>
-    <t>missing-hardening@api-server</t>
+    <t>missing-hardening@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Missing Hardening risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>missing-hardening@ecs-platform</t>
   </si>
   <si>
     <t>PostgreSQL Database</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>Missing Hardening risk at PostgreSQL Database</t>
   </si>
   <si>
     <t>missing-hardening@postgresql-db</t>
   </si>
   <si>
+    <t>CWE-22</t>
+  </si>
+  <si>
+    <t>Path-Traversal</t>
+  </si>
+  <si>
+    <t>MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>Path-Traversal Prevention</t>
+  </si>
+  <si>
+    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at ECS Container Platform against filesystem AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>path-traversal@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Push Image to Registry</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Path-Traversal risk at GitHub Actions Build Pipeline against filesystem AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>path-traversal@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>CWE-918</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF)</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>SSRF Prevention</t>
+  </si>
+  <si>
+    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+  </si>
+  <si>
+    <t>SES Email Send</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Lambda Email Notifier server-side web-requesting the target AWS SES via SES Email Send</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@lambda-notifier@aws-ses@lambda-notifier&gt;ses-email-send</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at ECS Container Platform server-side web-requesting the target AWS ECR Container Registry via Pull Images from ECR</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@ecs-platform@container-registry@ecs-platform&gt;pull-images-from-ecr</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at GitHub Actions Build Pipeline server-side web-requesting the target AWS ECR Container Registry via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@build-pipeline@container-registry@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>Push to Pipeline</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at VaultNote Source Repository server-side web-requesting the target GitHub Actions Build Pipeline via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@source-repo@build-pipeline@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Redis Cache</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Missing Hardening risk at Redis Cache</t>
-  </si>
-  <si>
-    <t>missing-hardening@redis-cache</t>
-  </si>
-  <si>
-    <t>CWE-22</t>
-  </si>
-  <si>
-    <t>Path-Traversal</t>
-  </si>
-  <si>
-    <t>MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal risk at API Server against filesystem MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>Path-Traversal Prevention</t>
-  </si>
-  <si>
-    <t>Before accessing the file cross-check that it resides in the expected folder and is of the expected type and filename/suffix. Try to use a mapping if possible instead of directly accessing by a filename which is (partly or fully) provided by the caller. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>path-traversal@api-server@minio-storage@api-server&gt;minio-file-storage</t>
-  </si>
-  <si>
-    <t>CWE-918</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF)</t>
-  </si>
-  <si>
-    <t>Server-Side Request Forgery (SSRF) risk at API Server server-side web-requesting the target MinIO Object Storage via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>SSRF Prevention</t>
-  </si>
-  <si>
-    <t>Try to avoid constructing the outgoing target URL with caller controllable values. Alternatively use a mapping (whitelist) when accessing outgoing URLs instead of creating them including caller controllable values. When a third-party product is used instead of custom developed software, check if the product applies the proper mitigation and ensure a reasonable patch-level.</t>
-  </si>
-  <si>
-    <t>server-side-request-forgery@api-server@minio-storage@api-server&gt;minio-file-storage</t>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target Note RAG Pipeline via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@rag-pipeline@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>Query Vector Store</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at LLM Note Summarizer server-side web-requesting the target VaultNote Vector Store via Query Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@llm-summarizer@vector-store@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
+    <t>Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Server-Side Request Forgery (SSRF) risk at Note RAG Pipeline server-side web-requesting the target VaultNote Vector Store via Retrieve from Vector Store</t>
+  </si>
+  <si>
+    <t>server-side-request-forgery@rag-pipeline@vector-store@rag-pipeline&gt;retrieve-from-vector-store</t>
   </si>
   <si>
     <t>CWE-319</t>
@@ -405,9 +827,6 @@
   </si>
   <si>
     <t>unencrypted-communication@nginx-proxy&gt;http-to-api-server@nginx-proxy@api-server</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <t xml:space="preserve">Migrating Nginx-to-API communication to mTLS. A separate CA will be provisioned inside the Docker network. PR #47 is in review; target completion sprint 22.
@@ -417,15 +836,57 @@
     <t>2026-04-18</t>
   </si>
   <si>
-    <t>Security Team</t>
-  </si>
-  <si>
     <t>VAULT-102</t>
   </si>
   <si>
     <t>CWE-501</t>
   </si>
   <si>
+    <t>Unguarded Access From Internet</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of API Server by AWS API Gateway via Route to ECS API</t>
+  </si>
+  <si>
+    <t>Encapsulation of Technical Asset</t>
+  </si>
+  <si>
+    <t>Encapsulate the asset behind a guarding service, application, or reverse-proxy. For admin maintenance a bastion-host should be used as a jump-server. For file transfer a store-and-forward-host should be used as an indirect file exchange platform.</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@api-server@aws-api-gateway@aws-api-gateway&gt;route-to-ecs-api</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of AWS ECR Container Registry by GitHub Actions Build Pipeline via Push Image to Registry</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@container-registry@build-pipeline@build-pipeline&gt;push-image-to-registry</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of GitHub Actions Build Pipeline by VaultNote Source Repository via Push to Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@build-pipeline@source-repo@source-repo&gt;push-to-pipeline</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of Note RAG Pipeline by LLM Note Summarizer via Call RAG Pipeline</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@rag-pipeline@llm-summarizer@llm-summarizer&gt;call-rag-pipeline</t>
+  </si>
+  <si>
+    <t>VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Unguarded Access from Internet of VaultNote Vector Store by LLM Note Summarizer via Query Vector Store</t>
+  </si>
+  <si>
+    <t>unguarded-access-from-internet@vector-store@llm-summarizer@llm-summarizer&gt;query-vector-store</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access</t>
   </si>
   <si>
@@ -441,21 +902,95 @@
     <t>unguarded-direct-datastore-access@api-server&gt;postgresql-connection@api-server@postgresql-db</t>
   </si>
   <si>
+    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
+  </si>
+  <si>
+    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+  </si>
+  <si>
+    <t>Redis Cache</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>Unguarded Direct Datastore Access of Redis Cache by API Server via Redis Session Store</t>
   </si>
   <si>
     <t>unguarded-direct-datastore-access@api-server&gt;redis-session-store@api-server@redis-cache</t>
   </si>
   <si>
-    <t>Unguarded Direct Datastore Access of MinIO Object Storage by API Server via MinIO File Storage</t>
-  </si>
-  <si>
-    <t>unguarded-direct-datastore-access@api-server&gt;minio-file-storage@api-server@minio-storage</t>
+    <t>CWE-200</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak</t>
+  </si>
+  <si>
+    <t>Accidental Secret Leak(Git) risk at VaultNote Source Repository: Git Leak Prevention</t>
+  </si>
+  <si>
+    <t>Build Pipeline Hardening</t>
+  </si>
+  <si>
+    <t>Establish measures preventing accidental check-in or package-in of secrets into sourcecode repositories and artifact registries. This starts by using good .gitignore and .dockerignore files, but does not stop there. See for example tools like &lt;i&gt;\"git-secrets\"&lt;/i&gt; or &lt;i&gt;\"Talisman\"&lt;/i&gt; to have check-in preventive measures for secrets. Consider also to regularly scan your repositories for secrets accidentally checked-in using scanning tools like &lt;i&gt;"gitleaks"&lt;/i&gt; or &lt;i&gt;"gitrob"&lt;/i&gt;.</t>
+  </si>
+  <si>
+    <t>accidental-secret-leak@source-repo</t>
+  </si>
+  <si>
+    <t>Cloud Storage - Object Storage Without Versioning for Strictly-Confidential Data</t>
+  </si>
+  <si>
+    <t>No Versioning: object storage AWS S3 Notes Bucket stores strictly-confidential data without versioning enabled</t>
+  </si>
+  <si>
+    <t>Enable versioning (and optionally object lock) on buckets holding strictly-confidential data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable S3 Versioning / GCS Object Versioning / Azure Blob versioning on all buckets storing strictly-confidential data. Consider enabling S3 Object Lock in compliance mode for regulatory records. Configure lifecycle rules to expire old versions after a retention window. Tag the asset has-versioning once deployed.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is bucket versioning enabled for all strictly-confidential data stores? Is object lock configured for data subject to regulatory retention requirements?
+</t>
+  </si>
+  <si>
+    <t>cloud-object-storage-no-versioning@s3-notes-bucket</t>
+  </si>
+  <si>
+    <t>No Versioning: object storage MinIO Object Storage stores strictly-confidential data without versioning enabled</t>
+  </si>
+  <si>
+    <t>cloud-object-storage-no-versioning@minio-storage</t>
   </si>
   <si>
     <t>CWE-912</t>
   </si>
   <si>
+    <t>Code Backdooring</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>Reduce the attack surface of backdooring the build pipeline by not directly exposing the build pipeline components on the public internet and also not exposing it in front of unmanaged (out-of-scope) developer clients.Also consider the use of code signing to prevent code modifications.</t>
+  </si>
+  <si>
+    <t>code-backdooring@container-registry</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>code-backdooring@build-pipeline</t>
+  </si>
+  <si>
+    <t>Code Backdooring risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>code-backdooring@source-repo</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring</t>
   </si>
   <si>
@@ -492,12 +1027,39 @@
     <t>container-baseimage-backdooring@minio-storage</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@rag-pipeline</t>
+  </si>
+  <si>
     <t>Container Base Image Backdooring risk at Redis Cache</t>
   </si>
   <si>
     <t>container-baseimage-backdooring@redis-cache</t>
   </si>
   <si>
+    <t>Container Base Image Backdooring risk at VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>container-baseimage-backdooring@vector-store</t>
+  </si>
+  <si>
+    <t>Container Platform Escape</t>
+  </si>
+  <si>
+    <t>Container Platform Escape risk at ECS Container Platform</t>
+  </si>
+  <si>
+    <t>Apply hardening of all container infrastructures. &lt;p&gt;See for example the &lt;i&gt;CIS-Benchmarks for Docker and Kubernetes&lt;/i&gt; as well as the &lt;i&gt;Docker Bench for Security&lt;/i&gt; ( &lt;a href="https://github.com/docker/docker-bench-security"&gt;https://github.com/docker/docker-bench-security&lt;/a&gt; ) or &lt;i&gt;InSpec Checks for Docker and Kubernetes&lt;/i&gt; ( &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-docker-benchmark&lt;/a&gt; and &lt;a href="https://github.com/dev-sec/cis-kubernetes-benchmark"&gt;https://github.com/dev-sec/cis-kubernetes-benchmark&lt;/a&gt; ). Use only trusted base images, verify digital signatures and apply image creation best practices. Also consider using Google's &lt;b&gt;Distroless&lt;/i&gt; base images or otherwise very small base images. Apply namespace isolation and nod affinity to separate pods from each other in terms of access and nodes the same style as you separate data.</t>
+  </si>
+  <si>
+    <t>Are recommendations from the linked cheat sheet and referenced ASVS or CSVS chapter applied?</t>
+  </si>
+  <si>
+    <t>container-platform-escape@ecs-platform</t>
+  </si>
+  <si>
     <t>CWE-1127</t>
   </si>
   <si>
@@ -505,9 +1067,6 @@
   </si>
   <si>
     <t>Missing Build Infrastructure in the threat model (referencing asset API Server as an example)</t>
-  </si>
-  <si>
-    <t>Build Pipeline Hardening</t>
   </si>
   <si>
     <t>Include the build infrastructure in the model.</t>
@@ -622,25 +1181,58 @@
     <t>2026-04-10</t>
   </si>
   <si>
-    <t>Infrastructure Team</t>
-  </si>
-  <si>
     <t>VAULT-95</t>
   </si>
   <si>
+    <t>Unchecked Deployment</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at GitHub Actions Build Pipeline</t>
+  </si>
+  <si>
+    <t>Apply DevSecOps best-practices and use scanning tools to identify vulnerabilities in source- or byte-code,dependencies, container layers, and optionally also via dynamic scans against running test systems.</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@build-pipeline</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at VaultNote Source Repository</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@source-repo</t>
+  </si>
+  <si>
+    <t>Unchecked Deployment risk at AWS ECR Container Registry</t>
+  </si>
+  <si>
+    <t>unchecked-deployment@container-registry</t>
+  </si>
+  <si>
     <t>CWE-311</t>
   </si>
   <si>
     <t>Unencrypted Technical Assets</t>
   </si>
   <si>
+    <t>Unencrypted Technical Asset named AWS RDS PostgreSQL missing end user individual encryption with data-with-end-user-individual-key</t>
+  </si>
+  <si>
+    <t>Encryption of Technical Asset</t>
+  </si>
+  <si>
+    <t>Apply encryption to the technical asset.</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Unencrypted Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unencrypted-asset@s3-notes-bucket</t>
+  </si>
+  <si>
     <t>Unencrypted Technical Asset named Redis Cache</t>
-  </si>
-  <si>
-    <t>Encryption of Technical Asset</t>
-  </si>
-  <si>
-    <t>Apply encryption to the technical asset.</t>
   </si>
   <si>
     <t>unencrypted-asset@redis-cache</t>
@@ -675,9 +1267,6 @@
     <t>VAULT-110</t>
   </si>
   <si>
-    <t>Denial of Service</t>
-  </si>
-  <si>
     <t>CWE-400</t>
   </si>
   <si>
@@ -709,6 +1298,27 @@
   </si>
   <si>
     <t>dos-risky-access-across-trust-boundary@postgresql-db@api-server@api-server&gt;postgresql-connection-&gt;</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>Attack Surface Reduction</t>
+  </si>
+  <si>
+    <t>Try to avoid using technical assets that do not process or store anything.</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Unnecessary Technical Asset named AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>unnecessary-technical-asset@s3-notes-bucket</t>
   </si>
 </sst>
 </file>
@@ -1240,12 +1850,12 @@
     <col customWidth="true" max="4" min="4" width="25.57142857142857"/>
     <col customWidth="true" max="5" min="5" width="17.857142857142854"/>
     <col customWidth="true" max="6" min="6" width="13.571428571428571"/>
-    <col customWidth="true" max="7" min="7" width="55.57142857142857"/>
-    <col customWidth="true" max="8" min="8" width="23.857142857142858"/>
-    <col customWidth="true" max="9" min="9" width="25"/>
+    <col customWidth="true" max="7" min="7" width="75.28571428571428"/>
+    <col customWidth="true" max="8" min="8" width="31.57142857142857"/>
+    <col customWidth="true" max="9" min="9" width="29"/>
     <col customWidth="true" max="10" min="10" width="12"/>
     <col customWidth="true" max="11" min="11" width="75"/>
-    <col customWidth="true" max="12" min="12" width="66.42857142857143"/>
+    <col customWidth="true" max="12" min="12" width="75.71428571428572"/>
     <col customWidth="true" max="13" min="13" width="75"/>
     <col customWidth="true" max="14" min="14" width="40"/>
     <col customWidth="true" max="15" min="15" width="92.14285714285714"/>
@@ -1258,25 +1868,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>15</v>
       </c>
       <c r="H1" s="24" t="s">
         <v>3</v>
@@ -1285,34 +1895,34 @@
         <v>4</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L1" s="24" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N1" s="24" t="s">
         <v>10</v>
       </c>
       <c r="O1" s="24" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q1" s="24" t="s">
         <v>1</v>
       </c>
       <c r="R1" s="24" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S1" s="24" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T1" s="24" t="s">
         <v>12</v>
@@ -1512,43 +2122,43 @@
         <v>52</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>53</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="18" t="s">
+      <c r="K5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="L5" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="M5" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="N5" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="O5" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="O5" s="20" t="s">
-        <v>63</v>
       </c>
       <c r="P5" s="10" t="s">
         <v>34</v>
@@ -1574,43 +2184,43 @@
         <v>52</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="K6" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="L6" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="20" t="s">
         <v>66</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>71</v>
       </c>
       <c r="P6" s="10" t="s">
         <v>34</v>
@@ -1633,46 +2243,46 @@
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="N7" s="23" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="P7" s="10" t="s">
         <v>34</v>
@@ -1701,40 +2311,40 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="N8" s="23" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="O8" s="20" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="P8" s="10" t="s">
         <v>34</v>
@@ -1763,40 +2373,40 @@
         <v>48</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>34</v>
@@ -1831,96 +2441,96 @@
         <v>23</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="T10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="5" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="18" t="s">
+      <c r="K11" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="L11" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="N10" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O10" s="20" t="s">
+      <c r="M11" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="P10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S10" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T10" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="N11" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="O11" s="20" t="s">
         <v>99</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>102</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>34</v>
@@ -1943,61 +2553,61 @@
         <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="M12" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="N12" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="19" t="s">
+      <c r="O12" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="L12" s="23" t="s">
+      <c r="P12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q12" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="R12" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="N12" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O12" s="20" t="s">
+      <c r="T12" s="16" t="s">
         <v>109</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T12" s="16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -2011,55 +2621,55 @@
         <v>48</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>34</v>
+        <v>117</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="T13" s="16" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -2073,40 +2683,40 @@
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>34</v>
@@ -2135,40 +2745,40 @@
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="N15" s="23" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>34</v>
@@ -2194,58 +2804,58 @@
         <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="N16" s="23" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>34</v>
+        <v>141</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="T16" s="16" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17">
@@ -2256,58 +2866,58 @@
         <v>52</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="M17" s="23" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="N17" s="23" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>128</v>
+        <v>149</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="R17" s="17" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -2318,58 +2928,58 @@
         <v>52</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="N18" s="23" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>34</v>
+        <v>151</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19">
@@ -2380,43 +2990,43 @@
         <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="N19" s="23" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="P19" s="10" t="s">
         <v>34</v>
@@ -2435,50 +3045,50 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>105</v>
+      <c r="C20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="M20" s="23" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="N20" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O20" s="20" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="P20" s="10" t="s">
         <v>34</v>
@@ -2497,50 +3107,50 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>27</v>
+      <c r="I21" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="J21" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>34</v>
@@ -2559,50 +3169,50 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="A22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="7" t="s">
+      <c r="F22" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="P22" s="10" t="s">
         <v>34</v>
@@ -2621,50 +3231,50 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="A23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="7" t="s">
+      <c r="F23" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>34</v>
@@ -2687,10 +3297,10 @@
         <v>48</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>35</v>
@@ -2699,34 +3309,34 @@
         <v>23</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="P24" s="10" t="s">
         <v>34</v>
@@ -2745,112 +3355,112 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="A25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="N25" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="O25" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="L25" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="M25" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="N25" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="O25" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S25" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="T25" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="F26" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="N26" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="P26" s="10" t="s">
         <v>34</v>
@@ -2869,50 +3479,50 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="7" t="s">
+      <c r="A27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="N27" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>34</v>
@@ -2931,50 +3541,50 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="A28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>41</v>
-      </c>
       <c r="K28" s="19" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="N28" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="P28" s="10" t="s">
         <v>34</v>
@@ -2993,50 +3603,50 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="A29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="7" t="s">
+      <c r="E29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>27</v>
+      <c r="I29" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J29" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="N29" s="23" t="s">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>34</v>
@@ -3055,50 +3665,50 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>27</v>
+      <c r="A30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="M30" s="23" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="N30" s="23" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="O30" s="20" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>34</v>
@@ -3117,112 +3727,112 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>27</v>
+      <c r="A31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M31" s="23" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="N31" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>196</v>
+        <v>217</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q31" s="19" t="s">
-        <v>197</v>
+        <v>27</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>198</v>
+        <v>27</v>
       </c>
       <c r="S31" s="17" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="A32" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>27</v>
+      <c r="E32" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="M32" s="23" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="N32" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="P32" s="10" t="s">
         <v>34</v>
@@ -3241,65 +3851,65 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="A33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>27</v>
+      <c r="E33" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="M33" s="23" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="N33" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>196</v>
+        <v>226</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="Q33" s="19" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="R33" s="17" t="s">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="S33" s="17" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="T33" s="16" t="s">
-        <v>211</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -3307,7 +3917,7 @@
         <v>48</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>48</v>
@@ -3316,87 +3926,87 @@
         <v>22</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="M34" s="23" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="N34" s="23" t="s">
         <v>45</v>
       </c>
       <c r="O34" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R34" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S34" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T34" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="P34" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q34" s="19" t="s">
+      <c r="I35" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="R34" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="S34" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="T34" s="16" t="s">
+      <c r="J35" s="18" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>41</v>
-      </c>
       <c r="K35" s="19" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="L35" s="23" t="s">
         <v>221</v>
@@ -3408,7 +4018,7 @@
         <v>45</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>34</v>
@@ -3427,38 +4037,38 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G36" s="9" t="s">
+      <c r="A36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>219</v>
       </c>
+      <c r="H36" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>232</v>
+      </c>
       <c r="J36" s="18" t="s">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="L36" s="23" t="s">
         <v>221</v>
@@ -3470,7 +4080,7 @@
         <v>45</v>
       </c>
       <c r="O36" s="20" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="P36" s="10" t="s">
         <v>34</v>
@@ -3489,38 +4099,38 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="G37" s="9" t="s">
+      <c r="A37" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H37" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>40</v>
+      <c r="G37" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>95</v>
+        <v>238</v>
       </c>
       <c r="K37" s="19" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="L37" s="23" t="s">
         <v>221</v>
@@ -3532,7 +4142,7 @@
         <v>45</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>34</v>
@@ -3550,8 +4160,2922 @@
         <v>27</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N38" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O38" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T38" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="N39" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="L40" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="P40" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T40" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J41" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q41" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T41" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J42" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="M42" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T42" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J43" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="M43" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q43" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="R43" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="S43" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="T43" s="16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="L44" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="M44" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O44" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="P44" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T44" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="L45" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="N45" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q45" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T45" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="L46" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="M46" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="P46" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q46" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="J47" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="L47" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="M47" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="N47" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q47" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T47" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K48" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="L48" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q48" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T48" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L49" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S49" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T49" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="L50" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="N50" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="P50" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T50" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J51" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="N51" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O51" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q51" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T51" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="L52" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O52" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="P52" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S52" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T52" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="L53" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="N53" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="O53" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T53" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="L54" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="O54" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q54" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T54" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="L55" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="N55" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O55" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T55" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="L56" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O56" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q56" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S56" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T56" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="N57" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O57" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S57" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T57" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="L58" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N58" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O58" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S58" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T58" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="L59" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N59" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O59" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S59" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T59" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J60" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="L60" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N60" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O60" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q60" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S60" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T60" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="L61" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N61" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O61" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q61" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="L62" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N62" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O62" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="P62" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q62" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T62" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N63" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O63" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q63" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S63" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T63" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="L64" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="N64" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="O64" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="P64" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q64" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T64" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="L65" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="N65" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="O65" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q65" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S65" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T65" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J66" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="L66" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="N66" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O66" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="P66" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q66" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T66" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J67" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="L67" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="N67" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O67" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q67" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T67" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J68" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K68" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="L68" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="N68" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O68" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q68" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S68" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T68" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J69" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K69" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="L69" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N69" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="O69" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q69" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S69" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T69" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J70" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="L70" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="N70" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="O70" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="P70" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q70" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R70" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S70" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T70" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="K71" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="L71" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="M71" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="N71" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O71" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="P71" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q71" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="R71" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="S71" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="T71" s="16" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K72" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="L72" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="N72" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O72" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q72" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R72" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S72" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T72" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="L73" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M73" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="N73" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O73" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q73" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T73" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K74" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="L74" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="N74" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O74" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="P74" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q74" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R74" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S74" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T74" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J75" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K75" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="L75" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M75" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N75" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O75" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q75" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R75" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S75" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T75" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J76" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="L76" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N76" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O76" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q76" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R76" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S76" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T76" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J77" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="K77" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L77" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M77" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N77" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O77" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q77" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R77" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S77" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T77" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J78" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K78" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="L78" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M78" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N78" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O78" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="P78" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q78" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="R78" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="S78" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="T78" s="16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J79" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K79" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="L79" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="M79" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N79" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O79" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="P79" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q79" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="R79" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="S79" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="T79" s="16" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="J80" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K80" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="L80" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="M80" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="N80" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O80" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="P80" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q80" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R80" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S80" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T80" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="J81" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="K81" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="L81" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="M81" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="N81" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O81" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q81" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R81" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S81" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T81" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J82" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K82" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="L82" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="M82" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="N82" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O82" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="P82" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q82" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R82" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S82" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T82" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J83" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="K83" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="L83" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="M83" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="N83" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O83" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q83" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R83" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S83" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T83" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J84" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K84" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="L84" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="M84" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="N84" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O84" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="P84" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q84" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R84" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S84" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="T84" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$37"/>
+  <autoFilter ref="$A$1:$T$84"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>
